--- a/task172/golden/q1_2027_renewal_quote.xlsx
+++ b/task172/golden/q1_2027_renewal_quote.xlsx
@@ -64,16 +64,16 @@
     <t>counsel's appointment notices</t>
   </si>
   <si>
-    <t>Fingerprint appointments for renewals received before September 2026 (median)</t>
+    <t>Fingerprint appointments for renewals received in 2024 and 2025 (median)</t>
   </si>
   <si>
     <t>4 weeks after receipt</t>
   </si>
   <si>
-    <t>Renewals filed in the quarter still pending on the day the filer's card expires</t>
-  </si>
-  <si>
-    <t>more than half</t>
+    <t>Renewals filed in the quarter that need a new fingerprint appointment, still pending on the day the filer's card expires</t>
+  </si>
+  <si>
+    <t>about nine in ten</t>
   </si>
   <si>
     <t>the forecast below</t>
@@ -91,13 +91,13 @@
     <t>How the wait was forecast</t>
   </si>
   <si>
-    <t>A renewal waits for its fingerprint appointment, or not where USCIS reuses fingerprints it already holds, and then for the officer's review. The review was estimated on every renewal counsel filed since January 2024, renewals still open at the export counted as still waiting.</t>
-  </si>
-  <si>
-    <t>Renewals filed since 30 October 2025 no longer extend the card (GM-07 3.1). A renewal still pending when the filer's card expires gets the team's expedite request; USCIS has accepted most of them and decided the renewal a median of about a week later. While appointments came about four weeks out, few renewals got that far; with appointments now set about 17 weeks out, more than half of the quarter's renewals will.</t>
-  </si>
-  <si>
-    <t>The quarter's renewals were simulated with the appointments now being set, each decided at the earlier of its normal decision and its card's expiry plus the expedite response, and the 80th percentile of the wait taken in months of 30.4 days, to the nearest half month (GM-07 4.3).</t>
+    <t>A renewal waits for its fingerprint appointment, or not where USCIS reuses fingerprints it already holds, and then for the officer's review. The review was estimated on every renewal counsel filed since January 2024, renewals still open at the export counted as still waiting. USCIS reused fingerprints for most (c)(9) renewals and sent most (c)(26) renewals to an appointment; about half the quarter's renewals are (c)(9), the 18-month cards issued from December 2025 coming due.</t>
+  </si>
+  <si>
+    <t>Renewals filed since 30 October 2025 no longer extend the card (GM-07 3.1). A renewal still pending when the filer's card expires gets the team's expedite request around that day; USCIS has accepted most of them and decided the renewal a median of about a week after the request, in busy months as in quiet ones. While appointments came four to five weeks out, few renewals got that far; with appointments now set about 17 weeks out, about nine in ten of the quarter's renewals that need one will.</t>
+  </si>
+  <si>
+    <t>The quarter's renewals were simulated with the appointments now being set, each decided at the earlier of its normal decision and the team's request plus the expedite response, and the 80th percentile of the wait taken in months of 30.4 days, to the nearest half month (GM-07 4.3).</t>
   </si>
   <si>
     <t>Waits run from the receipt date on USCIS's receipt notice (GM-07 2.3) to the date of the decision notice, approval or denial; renewals withdrawn before a decision are left out (GM-07 4.2).</t>
@@ -133,7 +133,7 @@
     <t>July to September 2027</t>
   </si>
   <si>
-    <t>Cards from HR's roster, counsel's approval notices, the case register and the green-card tracker, one per holder and last day; a spouse's sponsor from the register, the tracker, the roster's onboarding entry or Benefits.</t>
+    <t>Each current person's work permit (GM-07 1.3 and 1.4): the card USCIS approved most recently, from HR's roster, counsel's approval notices, the case register and the green-card tracker, in the category of the approval. A spouse is counted once, whether Global Mobility's records or Benefits' ID carries her card, and belongs to the household the register, the tracker, the roster's onboarding entry or Benefits names.</t>
   </si>
   <si>
     <t>Most rejected renewal packets were filed again within 30 days</t>
@@ -166,7 +166,7 @@
     <t>October 2025 to September 2026</t>
   </si>
   <si>
-    <t>Rejection notices counsel logged and those applicants forwarded to Global Mobility, one per case and notice date. Filed again means USCIS received the renewal again (GM-07 2.3), whoever filed it.</t>
+    <t>Rejection notices counsel logged and those applicants forwarded to Global Mobility, one per case and notice date. Filed again within 30 days means USCIS received the renewal again no later than the 30th day after the notice's date (GM-07 2.3 and 2.4), whoever filed it.</t>
   </si>
 </sst>
 </file>
@@ -665,12 +665,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="44" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="74" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="74" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="88" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -741,10 +741,10 @@
         <v>279</v>
       </c>
       <c r="C5" s="11">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D5" s="11">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -755,10 +755,10 @@
         <v>140</v>
       </c>
       <c r="C6" s="11">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="D6" s="11">
-        <v>346</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>63</v>
       </c>
       <c r="C7" s="11">
-        <v>825</v>
+        <v>771</v>
       </c>
       <c r="D7" s="11">
-        <v>888</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -783,13 +783,13 @@
         <v>482</v>
       </c>
       <c r="C8" s="12">
-        <v>1217</v>
+        <v>1140</v>
       </c>
       <c r="D8" s="12">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>35</v>
       </c>
@@ -838,10 +838,10 @@
         <v>41</v>
       </c>
       <c r="B5" s="11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C5" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -849,10 +849,10 @@
         <v>42</v>
       </c>
       <c r="B6" s="11">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C6" s="11">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -860,10 +860,10 @@
         <v>43</v>
       </c>
       <c r="B7" s="11">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C7" s="11">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -871,10 +871,10 @@
         <v>44</v>
       </c>
       <c r="B8" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -882,10 +882,10 @@
         <v>45</v>
       </c>
       <c r="B9" s="12">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C9" s="12">
-        <v>82</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.25">

--- a/task172/golden/q1_2027_renewal_quote.xlsx
+++ b/task172/golden/q1_2027_renewal_quote.xlsx
@@ -133,7 +133,7 @@
     <t>July to September 2027</t>
   </si>
   <si>
-    <t>Each current person's work permit (GM-07 1.3 and 1.4): the card USCIS approved most recently, from HR's roster, counsel's approval notices, the case register and the green-card tracker, in the category of the approval. A spouse is counted once, whether Global Mobility's records or Benefits' ID carries her card, and belongs to the household the register, the tracker, the roster's onboarding entry or Benefits names.</t>
+    <t>Each current person's work permit (GM-07 1.3 and 1.4): the card USCIS approved most recently, from HR's roster, counsel's approval notices, the case register and the green-card tracker, in the category of the approval. Each person is counted once under all her IDs: an employee under every ID HR's program roster gives him (one benefits enrollment), a spouse whether Global Mobility's records, Benefits' ID or her own employee ID carries her card (one card number); a spouse belongs to the household the register, the tracker, the roster's onboarding entry or Benefits names.</t>
   </si>
   <si>
     <t>Most rejected renewal packets were filed again within 30 days</t>
@@ -166,7 +166,7 @@
     <t>October 2025 to September 2026</t>
   </si>
   <si>
-    <t>Rejection notices counsel logged and those applicants forwarded to Global Mobility, one per case and notice date. Filed again within 30 days means USCIS received the renewal again no later than the 30th day after the notice's date (GM-07 2.3 and 2.4), whoever filed it.</t>
+    <t>Rejection notices counsel logged and those applicants forwarded to Global Mobility, one per renewal and notice date, dated after the renewal's first packet left the mailroom and before USCIS had the renewal (the others are rejections of applicants' own other filings). Filed again within 30 days means USCIS received the renewal again no later than the 30th day after the notice's date (GM-07 2.3 and 2.4), whoever filed it and whichever case the register holds it under.</t>
   </si>
 </sst>
 </file>
@@ -789,7 +789,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>35</v>
       </c>
@@ -888,7 +888,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="92" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>46</v>
       </c>
